--- a/Data/ModelResponse/3/evaluation/evaluation_summary.xlsx
+++ b/Data/ModelResponse/3/evaluation/evaluation_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,35 +453,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -506,28 +546,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.495</v>
+        <v>0.49609375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4946014011884907</v>
+        <v>0.49609375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4963720304168442</v>
+        <v>9554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4507094177190307</v>
+        <v>14927</v>
       </c>
       <c r="J2" t="n">
-        <v>7478</v>
+        <v>0.4959469417833456</v>
       </c>
       <c r="K2" t="n">
-        <v>2076</v>
+        <v>0.7748586979275696</v>
       </c>
       <c r="L2" t="n">
-        <v>7620</v>
+        <v>0.6047955557371023</v>
       </c>
       <c r="M2" t="n">
-        <v>2026</v>
+        <v>9646</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4273</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4966065995787503</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2199875596102011</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3049069617070191</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7403</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2151</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7524</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2122</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +641,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -630,28 +734,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.48125</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4853096179183136</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4930238814748078</v>
+        <v>387</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4105856683550192</v>
+        <v>701</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>0.4907275320970043</v>
       </c>
       <c r="K2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6323529411764706</v>
+      </c>
+      <c r="M2" t="n">
+        <v>413</v>
+      </c>
+      <c r="N2" t="n">
+        <v>99</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5656565656565656</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1355932203389831</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="R2" t="n">
+        <v>344</v>
+      </c>
+      <c r="S2" t="n">
+        <v>43</v>
+      </c>
+      <c r="T2" t="n">
+        <v>357</v>
+      </c>
+      <c r="U2" t="n">
         <v>56</v>
-      </c>
-      <c r="L2" t="n">
-        <v>359</v>
-      </c>
-      <c r="M2" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -673,27 +801,51 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5125</v>
+        <v>0.50875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5212478506509457</v>
+        <v>0.50875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5086508650865087</v>
+        <v>404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.425050123835358</v>
+        <v>705</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>0.5078014184397163</v>
       </c>
       <c r="K3" t="n">
-        <v>43</v>
+        <v>0.8861386138613861</v>
       </c>
       <c r="L3" t="n">
+        <v>0.6456266907123533</v>
+      </c>
+      <c r="M3" t="n">
+        <v>396</v>
+      </c>
+      <c r="N3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5157894736842106</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1237373737373737</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1995926680244399</v>
+      </c>
+      <c r="R3" t="n">
+        <v>358</v>
+      </c>
+      <c r="S3" t="n">
+        <v>46</v>
+      </c>
+      <c r="T3" t="n">
         <v>347</v>
       </c>
-      <c r="M3" t="n">
+      <c r="U3" t="n">
         <v>49</v>
       </c>
     </row>
@@ -716,28 +868,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.495</v>
+        <v>0.4725</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4906119392617967</v>
+        <v>0.4725</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4913354358237473</v>
+        <v>821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4829759596618867</v>
+        <v>851</v>
       </c>
       <c r="J4" t="n">
-        <v>518</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="K4" t="n">
-        <v>303</v>
+        <v>0.5042630937880633</v>
       </c>
       <c r="L4" t="n">
-        <v>505</v>
+        <v>0.4952153110047847</v>
       </c>
       <c r="M4" t="n">
-        <v>274</v>
+        <v>779</v>
+      </c>
+      <c r="N4" t="n">
+        <v>749</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4566088117489986</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4390243902439024</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4476439790575916</v>
+      </c>
+      <c r="R4" t="n">
+        <v>414</v>
+      </c>
+      <c r="S4" t="n">
+        <v>407</v>
+      </c>
+      <c r="T4" t="n">
+        <v>437</v>
+      </c>
+      <c r="U4" t="n">
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -759,28 +935,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.503125</v>
+        <v>0.5125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5019592476489028</v>
+        <v>0.5125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5012656744404078</v>
+        <v>805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4537581823545856</v>
+        <v>1267</v>
       </c>
       <c r="J5" t="n">
-        <v>643</v>
+        <v>0.5098658247829518</v>
       </c>
       <c r="K5" t="n">
-        <v>162</v>
+        <v>0.8024844720496894</v>
       </c>
       <c r="L5" t="n">
-        <v>633</v>
+        <v>0.6235521235521235</v>
       </c>
       <c r="M5" t="n">
-        <v>162</v>
+        <v>795</v>
+      </c>
+      <c r="N5" t="n">
+        <v>333</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5225225225225225</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2188679245283019</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3085106382978724</v>
+      </c>
+      <c r="R5" t="n">
+        <v>646</v>
+      </c>
+      <c r="S5" t="n">
+        <v>159</v>
+      </c>
+      <c r="T5" t="n">
+        <v>621</v>
+      </c>
+      <c r="U5" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="6">
@@ -802,28 +1002,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.50125</v>
+        <v>0.49875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4775101333155107</v>
+        <v>0.49875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4910555554686902</v>
+        <v>821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4055412051944375</v>
+        <v>1389</v>
       </c>
       <c r="J6" t="n">
-        <v>722</v>
+        <v>0.5068394528437725</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>0.8574908647990256</v>
       </c>
       <c r="L6" t="n">
-        <v>699</v>
+        <v>0.6371040723981901</v>
       </c>
       <c r="M6" t="n">
-        <v>80</v>
+        <v>779</v>
+      </c>
+      <c r="N6" t="n">
+        <v>211</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4454976303317535</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1206675224646983</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1898989898989899</v>
+      </c>
+      <c r="R6" t="n">
+        <v>704</v>
+      </c>
+      <c r="S6" t="n">
+        <v>117</v>
+      </c>
+      <c r="T6" t="n">
+        <v>685</v>
+      </c>
+      <c r="U6" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -845,28 +1069,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.47625</v>
+        <v>0.4825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5256410256410257</v>
+        <v>0.4825</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5076995600251414</v>
+        <v>740</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3871749165866813</v>
+        <v>1398</v>
       </c>
       <c r="J7" t="n">
-        <v>686</v>
+        <v>0.4685264663805436</v>
       </c>
       <c r="K7" t="n">
-        <v>54</v>
+        <v>0.8851351351351351</v>
       </c>
       <c r="L7" t="n">
-        <v>784</v>
+        <v>0.6127221702525725</v>
       </c>
       <c r="M7" t="n">
-        <v>76</v>
+        <v>860</v>
+      </c>
+      <c r="N7" t="n">
+        <v>202</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5792079207920792</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.136046511627907</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2203389830508475</v>
+      </c>
+      <c r="R7" t="n">
+        <v>655</v>
+      </c>
+      <c r="S7" t="n">
+        <v>85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>743</v>
+      </c>
+      <c r="U7" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -888,28 +1136,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.495</v>
+        <v>0.4875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5268027778800863</v>
+        <v>0.4875</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5102489832388947</v>
+        <v>769</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4130029295367409</v>
+        <v>1485</v>
       </c>
       <c r="J8" t="n">
-        <v>695</v>
+        <v>0.4828282828282828</v>
       </c>
       <c r="K8" t="n">
-        <v>74</v>
+        <v>0.9323797139141743</v>
       </c>
       <c r="L8" t="n">
-        <v>734</v>
+        <v>0.6362023070097604</v>
       </c>
       <c r="M8" t="n">
-        <v>97</v>
+        <v>831</v>
+      </c>
+      <c r="N8" t="n">
+        <v>115</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5478260869565217</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.07581227436823104</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1331923890063425</v>
+      </c>
+      <c r="R8" t="n">
+        <v>717</v>
+      </c>
+      <c r="S8" t="n">
+        <v>52</v>
+      </c>
+      <c r="T8" t="n">
+        <v>768</v>
+      </c>
+      <c r="U8" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -931,28 +1203,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.485625</v>
+        <v>0.500625</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4691432915442939</v>
+        <v>0.500625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4781663007649535</v>
+        <v>822</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4403680447093573</v>
+        <v>1249</v>
       </c>
       <c r="J9" t="n">
-        <v>616</v>
+        <v>0.5092073658927142</v>
       </c>
       <c r="K9" t="n">
-        <v>206</v>
+        <v>0.7737226277372263</v>
       </c>
       <c r="L9" t="n">
-        <v>617</v>
+        <v>0.6141960405601159</v>
       </c>
       <c r="M9" t="n">
-        <v>161</v>
+        <v>778</v>
+      </c>
+      <c r="N9" t="n">
+        <v>351</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4700854700854701</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2120822622107969</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2922940655447299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>636</v>
+      </c>
+      <c r="S9" t="n">
+        <v>186</v>
+      </c>
+      <c r="T9" t="n">
+        <v>613</v>
+      </c>
+      <c r="U9" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -974,28 +1270,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.51125</v>
+        <v>0.50875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5284201781332716</v>
+        <v>0.50875</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5091939798494962</v>
+        <v>804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.410299770567398</v>
+        <v>1478</v>
       </c>
       <c r="J10" t="n">
-        <v>740</v>
+        <v>0.5060893098782138</v>
       </c>
       <c r="K10" t="n">
-        <v>64</v>
+        <v>0.9303482587064676</v>
       </c>
       <c r="L10" t="n">
-        <v>718</v>
+        <v>0.6555652936021034</v>
       </c>
       <c r="M10" t="n">
-        <v>78</v>
+        <v>796</v>
+      </c>
+      <c r="N10" t="n">
+        <v>122</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5409836065573771</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08291457286432161</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1437908496732026</v>
+      </c>
+      <c r="R10" t="n">
+        <v>748</v>
+      </c>
+      <c r="S10" t="n">
+        <v>56</v>
+      </c>
+      <c r="T10" t="n">
+        <v>730</v>
+      </c>
+      <c r="U10" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1017,28 +1337,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4975</v>
+        <v>0.490625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4950086805555556</v>
+        <v>0.490625</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4953989647670726</v>
+        <v>812</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4863243440093535</v>
+        <v>1001</v>
       </c>
       <c r="J11" t="n">
-        <v>516</v>
+        <v>0.4985014985014985</v>
       </c>
       <c r="K11" t="n">
-        <v>296</v>
+        <v>0.6145320197044335</v>
       </c>
       <c r="L11" t="n">
-        <v>508</v>
+        <v>0.5504688361831218</v>
       </c>
       <c r="M11" t="n">
-        <v>280</v>
+        <v>788</v>
+      </c>
+      <c r="N11" t="n">
+        <v>599</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4774624373956594</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3629441624365482</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4124008651766402</v>
+      </c>
+      <c r="R11" t="n">
+        <v>499</v>
+      </c>
+      <c r="S11" t="n">
+        <v>313</v>
+      </c>
+      <c r="T11" t="n">
+        <v>502</v>
+      </c>
+      <c r="U11" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -1060,28 +1404,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.493125</v>
+        <v>0.495</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4964790869908335</v>
+        <v>0.495</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4979151559100798</v>
+        <v>788</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4385112239338917</v>
+        <v>1300</v>
       </c>
       <c r="J12" t="n">
-        <v>644</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="K12" t="n">
-        <v>144</v>
+        <v>0.8121827411167513</v>
       </c>
       <c r="L12" t="n">
-        <v>667</v>
+        <v>0.6130268199233716</v>
       </c>
       <c r="M12" t="n">
-        <v>145</v>
+        <v>812</v>
+      </c>
+      <c r="N12" t="n">
+        <v>300</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.187192118226601</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2733812949640287</v>
+      </c>
+      <c r="R12" t="n">
+        <v>640</v>
+      </c>
+      <c r="S12" t="n">
+        <v>148</v>
+      </c>
+      <c r="T12" t="n">
+        <v>660</v>
+      </c>
+      <c r="U12" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -1103,28 +1471,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.504375</v>
+        <v>0.515</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5019392033542978</v>
+        <v>0.515</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5017348331043666</v>
+        <v>813</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4895132552341186</v>
+        <v>1129</v>
       </c>
       <c r="J13" t="n">
-        <v>540</v>
+        <v>0.516386182462356</v>
       </c>
       <c r="K13" t="n">
-        <v>273</v>
+        <v>0.7170971709717097</v>
       </c>
       <c r="L13" t="n">
-        <v>520</v>
+        <v>0.6004119464469618</v>
       </c>
       <c r="M13" t="n">
-        <v>267</v>
+        <v>787</v>
+      </c>
+      <c r="N13" t="n">
+        <v>471</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5116772823779193</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3062261753494282</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3831478537360891</v>
+      </c>
+      <c r="R13" t="n">
+        <v>583</v>
+      </c>
+      <c r="S13" t="n">
+        <v>230</v>
+      </c>
+      <c r="T13" t="n">
+        <v>546</v>
+      </c>
+      <c r="U13" t="n">
+        <v>241</v>
       </c>
     </row>
     <row r="14">
@@ -1146,28 +1538,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.480625</v>
+        <v>0.485</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4845840774118526</v>
+        <v>0.485</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4854767628205128</v>
+        <v>768</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4751781280011178</v>
+        <v>974</v>
       </c>
       <c r="J14" t="n">
-        <v>466</v>
+        <v>0.471252566735113</v>
       </c>
       <c r="K14" t="n">
-        <v>302</v>
+        <v>0.59765625</v>
       </c>
       <c r="L14" t="n">
-        <v>529</v>
+        <v>0.5269804822043628</v>
       </c>
       <c r="M14" t="n">
-        <v>303</v>
+        <v>832</v>
+      </c>
+      <c r="N14" t="n">
+        <v>626</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5063897763578274</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3810096153846154</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4348422496570645</v>
+      </c>
+      <c r="R14" t="n">
+        <v>459</v>
+      </c>
+      <c r="S14" t="n">
+        <v>309</v>
+      </c>
+      <c r="T14" t="n">
+        <v>515</v>
+      </c>
+      <c r="U14" t="n">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,35 +1633,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -1270,28 +1726,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421875</v>
+        <v>0.4114583333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3993827160493827</v>
+        <v>0.4114583333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4466564852187193</v>
+        <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3615912290686876</v>
+        <v>156</v>
       </c>
       <c r="J2" t="n">
-        <v>70</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>0.5387755102040817</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>103</v>
+      </c>
+      <c r="N2" t="n">
+        <v>36</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1262135922330097</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1870503597122302</v>
+      </c>
+      <c r="R2" t="n">
+        <v>66</v>
+      </c>
+      <c r="S2" t="n">
+        <v>23</v>
+      </c>
+      <c r="T2" t="n">
+        <v>90</v>
+      </c>
+      <c r="U2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1316,25 +1796,49 @@
         <v>0.4479166666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4338863750628457</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4571521668295862</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4004948745139626</v>
+        <v>155</v>
       </c>
       <c r="J3" t="n">
-        <v>70</v>
+        <v>0.4580645161290323</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="L3" t="n">
-        <v>83</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2205882352941177</v>
+      </c>
+      <c r="R3" t="n">
+        <v>71</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>84</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1356,28 +1860,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4698343504795118</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4808203991130821</v>
+        <v>110</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4459489456159823</v>
+        <v>142</v>
       </c>
       <c r="J4" t="n">
-        <v>87</v>
+        <v>0.5492957746478874</v>
       </c>
       <c r="K4" t="n">
-        <v>23</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="L4" t="n">
-        <v>68</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>82</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="R4" t="n">
+        <v>78</v>
+      </c>
+      <c r="S4" t="n">
+        <v>32</v>
+      </c>
+      <c r="T4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1399,28 +1927,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4559210526315789</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4709169831795985</v>
+        <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4231146809460062</v>
+        <v>163</v>
       </c>
       <c r="J5" t="n">
-        <v>74</v>
+        <v>0.4907975460122699</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="M5" t="n">
+        <v>95</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="R5" t="n">
+        <v>80</v>
+      </c>
+      <c r="S5" t="n">
         <v>17</v>
+      </c>
+      <c r="T5" t="n">
+        <v>83</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1442,28 +1994,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.470700232705733</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4848914584924184</v>
+        <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>0.425003185930929</v>
+        <v>159</v>
       </c>
       <c r="J6" t="n">
-        <v>86</v>
+        <v>0.5345911949685535</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="L6" t="n">
-        <v>77</v>
+        <v>0.648854961832061</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>89</v>
+      </c>
+      <c r="N6" t="n">
+        <v>33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1685393258426966</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2459016393442623</v>
+      </c>
+      <c r="R6" t="n">
+        <v>85</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" t="n">
+        <v>74</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1485,28 +2061,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4701179130996608</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4799174989144594</v>
+        <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4305681985024226</v>
+        <v>140</v>
       </c>
       <c r="J7" t="n">
-        <v>72</v>
+        <v>0.4785714285714286</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>0.7127659574468085</v>
       </c>
       <c r="L7" t="n">
-        <v>79</v>
+        <v>0.5726495726495727</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>98</v>
+      </c>
+      <c r="N7" t="n">
+        <v>52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2551020408163265</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="R7" t="n">
+        <v>67</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>73</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1528,28 +2128,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.515625</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5456843940714908</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5284782608695653</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4723248322940985</v>
+        <v>142</v>
       </c>
       <c r="J8" t="n">
-        <v>77</v>
+        <v>0.4859154929577465</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>0.75</v>
       </c>
       <c r="L8" t="n">
-        <v>78</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>69</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T8" t="n">
+        <v>73</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -1571,28 +2195,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4931647300068353</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4956293706293706</v>
+        <v>104</v>
       </c>
       <c r="I9" t="n">
-        <v>0.456626061277224</v>
+        <v>146</v>
       </c>
       <c r="J9" t="n">
-        <v>83</v>
+        <v>0.5342465753424658</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>0.75</v>
       </c>
       <c r="L9" t="n">
-        <v>71</v>
+        <v>0.6240000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>88</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2985074626865672</v>
+      </c>
+      <c r="R9" t="n">
+        <v>78</v>
+      </c>
+      <c r="S9" t="n">
+        <v>26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>68</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1614,28 +2262,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4651515151515151</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4697235629662132</v>
+        <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4585012087026591</v>
+        <v>122</v>
       </c>
       <c r="J10" t="n">
+        <v>0.5573770491803278</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5964912280701753</v>
+      </c>
+      <c r="M10" t="n">
+        <v>86</v>
+      </c>
+      <c r="N10" t="n">
         <v>70</v>
       </c>
-      <c r="K10" t="n">
-        <v>36</v>
-      </c>
-      <c r="L10" t="n">
-        <v>62</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24</v>
+      <c r="O10" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3720930232558139</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="R10" t="n">
+        <v>68</v>
+      </c>
+      <c r="S10" t="n">
+        <v>38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>54</v>
+      </c>
+      <c r="U10" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -1657,28 +2329,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5677083333333334</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.613557779799818</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5677083333333333</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5191744863168694</v>
+        <v>154</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>0.616</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>38</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1979166666666667</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2835820895522388</v>
+      </c>
+      <c r="R11" t="n">
+        <v>77</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" t="n">
+        <v>77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1700,28 +2396,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.453125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4346938775510204</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>0.453125</v>
+        <v>96</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4116101917520357</v>
+        <v>155</v>
       </c>
       <c r="J12" t="n">
-        <v>69</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>0.78125</v>
       </c>
       <c r="L12" t="n">
-        <v>78</v>
+        <v>0.5976095617529881</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>37</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2406015037593985</v>
+      </c>
+      <c r="R12" t="n">
+        <v>75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21</v>
+      </c>
+      <c r="T12" t="n">
+        <v>80</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -1743,28 +2463,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4657485371771086</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4739583333333333</v>
+        <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4404270668013273</v>
+        <v>142</v>
       </c>
       <c r="J13" t="n">
-        <v>69</v>
+        <v>0.4436619718309859</v>
       </c>
       <c r="K13" t="n">
-        <v>27</v>
+        <v>0.65625</v>
       </c>
       <c r="L13" t="n">
-        <v>74</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1770833333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2328767123287672</v>
+      </c>
+      <c r="R13" t="n">
+        <v>63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>33</v>
+      </c>
+      <c r="T13" t="n">
+        <v>79</v>
+      </c>
+      <c r="U13" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1786,28 +2530,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4250917094644167</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4435724549574445</v>
+        <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4185342216838279</v>
+        <v>144</v>
       </c>
       <c r="J14" t="n">
-        <v>77</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="L14" t="n">
-        <v>68</v>
+        <v>0.5928853754940712</v>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1686746987951807</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2137404580152672</v>
+      </c>
+      <c r="R14" t="n">
+        <v>75</v>
+      </c>
+      <c r="S14" t="n">
+        <v>34</v>
+      </c>
+      <c r="T14" t="n">
+        <v>69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1832,25 +2600,49 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.506043956043956</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.504776378636561</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4748717948717949</v>
+        <v>158</v>
       </c>
       <c r="J15" t="n">
-        <v>69</v>
+        <v>0.4936708860759494</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="M15" t="n">
-        <v>27</v>
+        <v>98</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="R15" t="n">
+        <v>78</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>80</v>
+      </c>
+      <c r="U15" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1872,28 +2664,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5344047811339041</v>
+        <v>0.515625</v>
       </c>
       <c r="H16" t="n">
-        <v>0.523202614379085</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4707367321475205</v>
+        <v>141</v>
       </c>
       <c r="J16" t="n">
-        <v>73</v>
+        <v>0.4893617021276596</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>0.5974025974025974</v>
       </c>
       <c r="M16" t="n">
-        <v>24</v>
+        <v>102</v>
+      </c>
+      <c r="N16" t="n">
+        <v>51</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3921568627450981</v>
+      </c>
+      <c r="R16" t="n">
+        <v>69</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>72</v>
+      </c>
+      <c r="U16" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1915,28 +2731,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5680117388114454</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5515515515515516</v>
+        <v>81</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4945670437997087</v>
+        <v>127</v>
       </c>
       <c r="J17" t="n">
-        <v>66</v>
+        <v>0.4409448818897638</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>0.691358024691358</v>
       </c>
       <c r="L17" t="n">
-        <v>79</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="M17" t="n">
-        <v>32</v>
+        <v>111</v>
+      </c>
+      <c r="N17" t="n">
+        <v>65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3603603603603603</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="R17" t="n">
+        <v>56</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1958,28 +2798,52 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4347658260422028</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4444991789819376</v>
+        <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4293464146587794</v>
+        <v>141</v>
       </c>
       <c r="J18" t="n">
-        <v>68</v>
+        <v>0.5390070921985816</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>0.7238095238095238</v>
       </c>
       <c r="L18" t="n">
-        <v>66</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="M18" t="n">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="N18" t="n">
+        <v>51</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4313725490196079</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2528735632183908</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.318840579710145</v>
+      </c>
+      <c r="R18" t="n">
+        <v>76</v>
+      </c>
+      <c r="S18" t="n">
+        <v>29</v>
+      </c>
+      <c r="T18" t="n">
+        <v>65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -2004,24 +2868,48 @@
         <v>0.453125</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4392109500805152</v>
+        <v>0.453125</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4508410200759631</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4242467513922605</v>
+        <v>138</v>
       </c>
       <c r="J19" t="n">
+        <v>0.4710144927536232</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6701030927835051</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="M19" t="n">
+        <v>95</v>
+      </c>
+      <c r="N19" t="n">
+        <v>54</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2315789473684211</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2953020134228188</v>
+      </c>
+      <c r="R19" t="n">
         <v>65</v>
       </c>
-      <c r="K19" t="n">
+      <c r="S19" t="n">
         <v>32</v>
       </c>
-      <c r="L19" t="n">
+      <c r="T19" t="n">
         <v>73</v>
       </c>
-      <c r="M19" t="n">
+      <c r="U19" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2047,25 +2935,49 @@
         <v>0.453125</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5131016042780749</v>
+        <v>0.453125</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5054161600530562</v>
+        <v>83</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3917267597984492</v>
+        <v>174</v>
       </c>
       <c r="J20" t="n">
-        <v>74</v>
+        <v>0.4367816091954023</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="L20" t="n">
-        <v>96</v>
+        <v>0.5914396887159533</v>
       </c>
       <c r="M20" t="n">
-        <v>13</v>
+        <v>109</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1009174311926606</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1732283464566929</v>
+      </c>
+      <c r="R20" t="n">
+        <v>76</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2090,25 +3002,49 @@
         <v>0.484375</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4625</v>
+        <v>0.484375</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4752362333007494</v>
+        <v>99</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4306083934936943</v>
+        <v>158</v>
       </c>
       <c r="J21" t="n">
-        <v>76</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>23</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="L21" t="n">
-        <v>76</v>
+        <v>0.6147859922178989</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>93</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1505376344086022</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2204724409448819</v>
+      </c>
+      <c r="R21" t="n">
+        <v>79</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="n">
+        <v>79</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -2130,28 +3066,52 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5240134028294863</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5143476810143477</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4293464146587794</v>
+        <v>151</v>
       </c>
       <c r="J22" t="n">
-        <v>68</v>
+        <v>0.423841059602649</v>
       </c>
       <c r="K22" t="n">
-        <v>13</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="L22" t="n">
-        <v>90</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>111</v>
+      </c>
+      <c r="N22" t="n">
+        <v>41</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5853658536585366</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="R22" t="n">
+        <v>64</v>
+      </c>
+      <c r="S22" t="n">
+        <v>17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>87</v>
+      </c>
+      <c r="U22" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -2173,28 +3133,52 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.546875</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5659154929577465</v>
+        <v>0.546875</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5515873015873016</v>
+        <v>84</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5053209364848213</v>
+        <v>133</v>
       </c>
       <c r="J23" t="n">
-        <v>67</v>
+        <v>0.4887218045112782</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>0.599078341013825</v>
       </c>
       <c r="M23" t="n">
-        <v>33</v>
+        <v>108</v>
+      </c>
+      <c r="N23" t="n">
+        <v>59</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.6779661016949152</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3703703703703703</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4790419161676647</v>
+      </c>
+      <c r="R23" t="n">
+        <v>65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>19</v>
+      </c>
+      <c r="T23" t="n">
+        <v>68</v>
+      </c>
+      <c r="U23" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -2216,28 +3200,52 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4825174825174825</v>
+        <v>88</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4222222222222222</v>
+        <v>160</v>
       </c>
       <c r="J24" t="n">
-        <v>68</v>
+        <v>0.4625</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="L24" t="n">
-        <v>84</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>104</v>
+      </c>
+      <c r="N24" t="n">
+        <v>32</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1730769230769231</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="R24" t="n">
+        <v>74</v>
+      </c>
+      <c r="S24" t="n">
+        <v>14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>86</v>
+      </c>
+      <c r="U24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -2262,25 +3270,49 @@
         <v>0.515625</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5102739726027397</v>
+        <v>0.515625</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5074942978168784</v>
+        <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4756717075319337</v>
+        <v>138</v>
       </c>
       <c r="J25" t="n">
-        <v>76</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K25" t="n">
-        <v>23</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L25" t="n">
-        <v>70</v>
+        <v>0.6075949367088608</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>93</v>
+      </c>
+      <c r="N25" t="n">
+        <v>54</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3673469387755102</v>
+      </c>
+      <c r="R25" t="n">
+        <v>72</v>
+      </c>
+      <c r="S25" t="n">
+        <v>27</v>
+      </c>
+      <c r="T25" t="n">
+        <v>66</v>
+      </c>
+      <c r="U25" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -2302,28 +3334,52 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4683098591549296</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4753694581280788</v>
+        <v>87</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4320326806592477</v>
+        <v>161</v>
       </c>
       <c r="J26" t="n">
-        <v>62</v>
+        <v>0.4596273291925466</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>0.8505747126436781</v>
       </c>
       <c r="L26" t="n">
-        <v>80</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>105</v>
+      </c>
+      <c r="N26" t="n">
+        <v>31</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="R26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>87</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -2345,28 +3401,52 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.53125</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5248713550600344</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5141986726145142</v>
+        <v>101</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4640198511166254</v>
+        <v>158</v>
       </c>
       <c r="J27" t="n">
-        <v>85</v>
+        <v>0.5506329113924051</v>
       </c>
       <c r="K27" t="n">
-        <v>16</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="L27" t="n">
-        <v>74</v>
+        <v>0.6718146718146718</v>
       </c>
       <c r="M27" t="n">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="N27" t="n">
+        <v>34</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.2197802197802198</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R27" t="n">
+        <v>87</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14</v>
+      </c>
+      <c r="T27" t="n">
+        <v>71</v>
+      </c>
+      <c r="U27" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -2388,28 +3468,52 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4525023169601483</v>
+        <v>0.46875</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4777536625067824</v>
+        <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3959443042706289</v>
+        <v>161</v>
       </c>
       <c r="J28" t="n">
-        <v>80</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="L28" t="n">
-        <v>86</v>
+        <v>0.6015625</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>97</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.134020618556701</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.203125</v>
+      </c>
+      <c r="R28" t="n">
+        <v>77</v>
+      </c>
+      <c r="S28" t="n">
+        <v>18</v>
+      </c>
+      <c r="T28" t="n">
+        <v>84</v>
+      </c>
+      <c r="U28" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -2431,28 +3535,52 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5323084126736383</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5225490196078432</v>
+        <v>90</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4736690232289713</v>
+        <v>148</v>
       </c>
       <c r="J29" t="n">
-        <v>72</v>
+        <v>0.4662162162162162</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>0.5798319327731093</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>102</v>
+      </c>
+      <c r="N29" t="n">
+        <v>44</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.2254901960784314</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.315068493150685</v>
+      </c>
+      <c r="R29" t="n">
+        <v>69</v>
+      </c>
+      <c r="S29" t="n">
+        <v>21</v>
+      </c>
+      <c r="T29" t="n">
+        <v>79</v>
+      </c>
+      <c r="U29" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -2474,28 +3602,52 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4892149669845928</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4920169436298469</v>
+        <v>99</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4604215456674473</v>
+        <v>150</v>
       </c>
       <c r="J30" t="n">
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7676767676767676</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6104417670682731</v>
+      </c>
+      <c r="M30" t="n">
+        <v>93</v>
+      </c>
+      <c r="N30" t="n">
+        <v>42</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4523809523809524</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.2043010752688172</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2814814814814815</v>
+      </c>
+      <c r="R30" t="n">
+        <v>76</v>
+      </c>
+      <c r="S30" t="n">
+        <v>23</v>
+      </c>
+      <c r="T30" t="n">
         <v>74</v>
       </c>
-      <c r="K30" t="n">
-        <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>71</v>
-      </c>
-      <c r="M30" t="n">
-        <v>22</v>
+      <c r="U30" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -2517,28 +3669,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4516008935219658</v>
+        <v>0.453125</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4717391304347826</v>
+        <v>92</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4039402985074627</v>
+        <v>145</v>
       </c>
       <c r="J31" t="n">
-        <v>73</v>
+        <v>0.4551724137931035</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="L31" t="n">
-        <v>85</v>
+        <v>0.5569620253164557</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>100</v>
+      </c>
+      <c r="N31" t="n">
+        <v>47</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R31" t="n">
+        <v>66</v>
+      </c>
+      <c r="S31" t="n">
+        <v>26</v>
+      </c>
+      <c r="T31" t="n">
+        <v>79</v>
+      </c>
+      <c r="U31" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="32">
@@ -2560,28 +3736,52 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6068376068376069</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6022690083996945</v>
+        <v>89</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5915784880549798</v>
+        <v>125</v>
       </c>
       <c r="J32" t="n">
-        <v>64</v>
+        <v>0.504</v>
       </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="L32" t="n">
-        <v>53</v>
+        <v>0.5887850467289719</v>
       </c>
       <c r="M32" t="n">
-        <v>50</v>
+        <v>103</v>
+      </c>
+      <c r="N32" t="n">
+        <v>67</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6119402985074627</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.3980582524271845</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.4823529411764705</v>
+      </c>
+      <c r="R32" t="n">
+        <v>63</v>
+      </c>
+      <c r="S32" t="n">
+        <v>26</v>
+      </c>
+      <c r="T32" t="n">
+        <v>62</v>
+      </c>
+      <c r="U32" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -2603,28 +3803,52 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4729965156794425</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4865392965696917</v>
+        <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4093761535622001</v>
+        <v>158</v>
       </c>
       <c r="J33" t="n">
-        <v>79</v>
+        <v>0.4936708860759494</v>
       </c>
       <c r="K33" t="n">
-        <v>15</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="L33" t="n">
-        <v>85</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="M33" t="n">
-        <v>13</v>
+        <v>98</v>
+      </c>
+      <c r="N33" t="n">
+        <v>34</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="R33" t="n">
+        <v>78</v>
+      </c>
+      <c r="S33" t="n">
+        <v>16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>80</v>
+      </c>
+      <c r="U33" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -2649,25 +3873,49 @@
         <v>0.515625</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5254154447702835</v>
+        <v>93</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4688085676037483</v>
+        <v>154</v>
       </c>
       <c r="J34" t="n">
-        <v>78</v>
+        <v>0.5</v>
       </c>
       <c r="K34" t="n">
-        <v>15</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="L34" t="n">
-        <v>78</v>
+        <v>0.6234817813765182</v>
       </c>
       <c r="M34" t="n">
-        <v>21</v>
+        <v>99</v>
+      </c>
+      <c r="N34" t="n">
+        <v>38</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.3211678832116788</v>
+      </c>
+      <c r="R34" t="n">
+        <v>77</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16</v>
+      </c>
+      <c r="T34" t="n">
+        <v>77</v>
+      </c>
+      <c r="U34" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -2689,28 +3937,52 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5100145372314651</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5067391304347826</v>
+        <v>92</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4564398914280711</v>
+        <v>156</v>
       </c>
       <c r="J35" t="n">
-        <v>73</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="K35" t="n">
-        <v>19</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="L35" t="n">
-        <v>78</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="M35" t="n">
-        <v>22</v>
+        <v>100</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="R35" t="n">
+        <v>72</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="n">
+        <v>84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -2732,28 +4004,52 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5211640211640212</v>
+        <v>84</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4709851551956815</v>
+        <v>133</v>
       </c>
       <c r="J36" t="n">
-        <v>65</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="K36" t="n">
-        <v>19</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="L36" t="n">
-        <v>79</v>
+        <v>0.5622119815668203</v>
       </c>
       <c r="M36" t="n">
-        <v>29</v>
+        <v>108</v>
+      </c>
+      <c r="N36" t="n">
+        <v>59</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.6101694915254238</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4311377245508982</v>
+      </c>
+      <c r="R36" t="n">
+        <v>61</v>
+      </c>
+      <c r="S36" t="n">
+        <v>23</v>
+      </c>
+      <c r="T36" t="n">
+        <v>72</v>
+      </c>
+      <c r="U36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -2775,28 +4071,52 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4791304347826087</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4491803278688524</v>
+        <v>145</v>
       </c>
       <c r="J37" t="n">
+        <v>0.496551724137931</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.5877551020408164</v>
+      </c>
+      <c r="M37" t="n">
+        <v>92</v>
+      </c>
+      <c r="N37" t="n">
+        <v>47</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4042553191489361</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.2065217391304348</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2733812949640287</v>
+      </c>
+      <c r="R37" t="n">
+        <v>72</v>
+      </c>
+      <c r="S37" t="n">
+        <v>28</v>
+      </c>
+      <c r="T37" t="n">
         <v>73</v>
       </c>
-      <c r="K37" t="n">
-        <v>27</v>
-      </c>
-      <c r="L37" t="n">
-        <v>71</v>
-      </c>
-      <c r="M37" t="n">
-        <v>21</v>
+      <c r="U37" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -2818,28 +4138,52 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.484375</v>
+        <v>0.53125</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4663147310206134</v>
+        <v>0.53125</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4781806339557099</v>
+        <v>98</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4306083934936944</v>
+        <v>146</v>
       </c>
       <c r="J38" t="n">
-        <v>76</v>
+        <v>0.5273972602739726</v>
       </c>
       <c r="K38" t="n">
-        <v>22</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="L38" t="n">
+        <v>0.6311475409836066</v>
+      </c>
+      <c r="M38" t="n">
+        <v>94</v>
+      </c>
+      <c r="N38" t="n">
+        <v>46</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.2659574468085106</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.3571428571428571</v>
+      </c>
+      <c r="R38" t="n">
         <v>77</v>
       </c>
-      <c r="M38" t="n">
-        <v>17</v>
+      <c r="S38" t="n">
+        <v>21</v>
+      </c>
+      <c r="T38" t="n">
+        <v>69</v>
+      </c>
+      <c r="U38" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="39">
@@ -2861,28 +4205,52 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5099773242630385</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5072751322751323</v>
+        <v>84</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4513199219081572</v>
+        <v>147</v>
       </c>
       <c r="J39" t="n">
-        <v>65</v>
+        <v>0.4625850340136055</v>
       </c>
       <c r="K39" t="n">
-        <v>19</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L39" t="n">
-        <v>82</v>
+        <v>0.5887445887445887</v>
       </c>
       <c r="M39" t="n">
-        <v>26</v>
+        <v>108</v>
+      </c>
+      <c r="N39" t="n">
+        <v>45</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6444444444444445</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.2685185185185185</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3790849673202615</v>
+      </c>
+      <c r="R39" t="n">
+        <v>68</v>
+      </c>
+      <c r="S39" t="n">
+        <v>16</v>
+      </c>
+      <c r="T39" t="n">
+        <v>79</v>
+      </c>
+      <c r="U39" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="40">
@@ -2904,28 +4272,52 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4102820746132848</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4464828484585323</v>
+        <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>0.387140902872777</v>
+        <v>156</v>
       </c>
       <c r="J40" t="n">
-        <v>75</v>
+        <v>0.4935897435897436</v>
       </c>
       <c r="K40" t="n">
-        <v>23</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="L40" t="n">
-        <v>82</v>
+        <v>0.6062992125984252</v>
       </c>
       <c r="M40" t="n">
-        <v>12</v>
+        <v>94</v>
+      </c>
+      <c r="N40" t="n">
+        <v>36</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.1595744680851064</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="R40" t="n">
+        <v>77</v>
+      </c>
+      <c r="S40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T40" t="n">
+        <v>79</v>
+      </c>
+      <c r="U40" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2947,28 +4339,52 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4237906905993307</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4725779967159278</v>
+        <v>105</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3875390253834667</v>
+        <v>144</v>
       </c>
       <c r="J41" t="n">
-        <v>92</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="K41" t="n">
-        <v>13</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="L41" t="n">
-        <v>81</v>
+        <v>0.5943775100401606</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>87</v>
+      </c>
+      <c r="N41" t="n">
+        <v>48</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.1954022988505747</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2518518518518518</v>
+      </c>
+      <c r="R41" t="n">
+        <v>74</v>
+      </c>
+      <c r="S41" t="n">
+        <v>31</v>
+      </c>
+      <c r="T41" t="n">
+        <v>70</v>
+      </c>
+      <c r="U41" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -2990,28 +4406,52 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4920351726774563</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H42" t="n">
-        <v>0.493182066106687</v>
+        <v>89</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4661327994661328</v>
+        <v>126</v>
       </c>
       <c r="J42" t="n">
-        <v>61</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="K42" t="n">
-        <v>28</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="L42" t="n">
-        <v>72</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="M42" t="n">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="N42" t="n">
+        <v>66</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.5606060606060606</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.3592233009708738</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4378698224852071</v>
+      </c>
+      <c r="R42" t="n">
+        <v>60</v>
+      </c>
+      <c r="S42" t="n">
+        <v>29</v>
+      </c>
+      <c r="T42" t="n">
+        <v>66</v>
+      </c>
+      <c r="U42" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="43">
@@ -3033,28 +4473,52 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.453125</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4299516908212561</v>
+        <v>0.453125</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4433347807207989</v>
+        <v>98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4173156207054511</v>
+        <v>137</v>
       </c>
       <c r="J43" t="n">
+        <v>0.4744525547445255</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.6632653061224489</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="M43" t="n">
+        <v>94</v>
+      </c>
+      <c r="N43" t="n">
+        <v>55</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.2340425531914894</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.2953020134228188</v>
+      </c>
+      <c r="R43" t="n">
         <v>65</v>
       </c>
-      <c r="K43" t="n">
+      <c r="S43" t="n">
         <v>33</v>
       </c>
-      <c r="L43" t="n">
-        <v>73</v>
-      </c>
-      <c r="M43" t="n">
-        <v>21</v>
+      <c r="T43" t="n">
+        <v>72</v>
+      </c>
+      <c r="U43" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -3076,28 +4540,52 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4866242038216561</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4918251584918252</v>
+        <v>111</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4565105506948018</v>
+        <v>157</v>
       </c>
       <c r="J44" t="n">
-        <v>90</v>
+        <v>0.5796178343949044</v>
       </c>
       <c r="K44" t="n">
-        <v>21</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="L44" t="n">
-        <v>67</v>
+        <v>0.6791044776119403</v>
       </c>
       <c r="M44" t="n">
-        <v>14</v>
+        <v>81</v>
+      </c>
+      <c r="N44" t="n">
+        <v>35</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.2586206896551724</v>
+      </c>
+      <c r="R44" t="n">
+        <v>91</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="n">
+        <v>66</v>
+      </c>
+      <c r="U44" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -3119,28 +4607,52 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5684523809523809</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5299511665762344</v>
+        <v>95</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4509631398673914</v>
+        <v>161</v>
       </c>
       <c r="J45" t="n">
-        <v>86</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="L45" t="n">
-        <v>82</v>
+        <v>0.65625</v>
       </c>
       <c r="M45" t="n">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="N45" t="n">
+        <v>31</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.2061855670103093</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.3124999999999999</v>
+      </c>
+      <c r="R45" t="n">
+        <v>84</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="n">
+        <v>77</v>
+      </c>
+      <c r="U45" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -3162,28 +4674,52 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.578125</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5977252047315742</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5584967320261438</v>
+        <v>102</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5196293436293435</v>
+        <v>168</v>
       </c>
       <c r="J46" t="n">
-        <v>89</v>
+        <v>0.5595238095238095</v>
       </c>
       <c r="K46" t="n">
-        <v>13</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="L46" t="n">
-        <v>68</v>
+        <v>0.6962962962962962</v>
       </c>
       <c r="M46" t="n">
-        <v>22</v>
+        <v>90</v>
+      </c>
+      <c r="N46" t="n">
+        <v>24</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.1777777777777778</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="R46" t="n">
+        <v>94</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" t="n">
+        <v>74</v>
+      </c>
+      <c r="U46" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -3205,28 +4741,52 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4866742044903893</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4910394265232975</v>
+        <v>99</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4497910447761194</v>
+        <v>165</v>
       </c>
       <c r="J47" t="n">
-        <v>77</v>
+        <v>0.496969696969697</v>
       </c>
       <c r="K47" t="n">
-        <v>22</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="L47" t="n">
-        <v>74</v>
+        <v>0.6212121212121211</v>
       </c>
       <c r="M47" t="n">
-        <v>19</v>
+        <v>93</v>
+      </c>
+      <c r="N47" t="n">
+        <v>27</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.3703703703703703</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.1075268817204301</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="R47" t="n">
+        <v>82</v>
+      </c>
+      <c r="S47" t="n">
+        <v>17</v>
+      </c>
+      <c r="T47" t="n">
+        <v>83</v>
+      </c>
+      <c r="U47" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -3248,28 +4808,52 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4960367125573634</v>
+        <v>0.5</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4969045291625937</v>
+        <v>93</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4639316239316239</v>
+        <v>151</v>
       </c>
       <c r="J48" t="n">
-        <v>68</v>
+        <v>0.4900662251655629</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="L48" t="n">
-        <v>73</v>
+        <v>0.6065573770491803</v>
       </c>
       <c r="M48" t="n">
-        <v>26</v>
+        <v>99</v>
+      </c>
+      <c r="N48" t="n">
+        <v>41</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="R48" t="n">
+        <v>74</v>
+      </c>
+      <c r="S48" t="n">
+        <v>19</v>
+      </c>
+      <c r="T48" t="n">
+        <v>77</v>
+      </c>
+      <c r="U48" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -3291,28 +4875,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5072598659717051</v>
+        <v>0.484375</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5042692939244663</v>
+        <v>87</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4305681985024225</v>
+        <v>136</v>
       </c>
       <c r="J49" t="n">
-        <v>72</v>
+        <v>0.4558823529411765</v>
       </c>
       <c r="K49" t="n">
-        <v>15</v>
+        <v>0.7126436781609196</v>
       </c>
       <c r="L49" t="n">
-        <v>86</v>
+        <v>0.5560538116591929</v>
       </c>
       <c r="M49" t="n">
-        <v>19</v>
+        <v>105</v>
+      </c>
+      <c r="N49" t="n">
+        <v>56</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.5535714285714286</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.2952380952380952</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.3850931677018634</v>
+      </c>
+      <c r="R49" t="n">
+        <v>62</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="n">
+        <v>74</v>
+      </c>
+      <c r="U49" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -3334,28 +4942,52 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5007279344858963</v>
+        <v>0.484375</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5004370629370629</v>
+        <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4305681985024226</v>
+        <v>153</v>
       </c>
       <c r="J50" t="n">
-        <v>72</v>
+        <v>0.4640522875816994</v>
       </c>
       <c r="K50" t="n">
-        <v>16</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="L50" t="n">
-        <v>85</v>
+        <v>0.5892116182572614</v>
       </c>
       <c r="M50" t="n">
-        <v>19</v>
+        <v>104</v>
+      </c>
+      <c r="N50" t="n">
+        <v>39</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.2115384615384615</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="R50" t="n">
+        <v>71</v>
+      </c>
+      <c r="S50" t="n">
+        <v>17</v>
+      </c>
+      <c r="T50" t="n">
+        <v>82</v>
+      </c>
+      <c r="U50" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -3377,28 +5009,52 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5754716981132075</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5432692307692307</v>
+        <v>88</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4723248322940985</v>
+        <v>170</v>
       </c>
       <c r="J51" t="n">
-        <v>77</v>
+        <v>0.488235294117647</v>
       </c>
       <c r="K51" t="n">
-        <v>11</v>
+        <v>0.9431818181818182</v>
       </c>
       <c r="L51" t="n">
-        <v>82</v>
+        <v>0.6434108527131783</v>
       </c>
       <c r="M51" t="n">
+        <v>104</v>
+      </c>
+      <c r="N51" t="n">
         <v>22</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.1634615384615385</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.2698412698412698</v>
+      </c>
+      <c r="R51" t="n">
+        <v>83</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>87</v>
+      </c>
+      <c r="U51" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -3420,28 +5076,52 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5546026300743282</v>
+        <v>0.5</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5311176278918215</v>
+        <v>93</v>
       </c>
       <c r="I52" t="n">
-        <v>0.468975468975469</v>
+        <v>165</v>
       </c>
       <c r="J52" t="n">
-        <v>80</v>
+        <v>0.4909090909090909</v>
       </c>
       <c r="K52" t="n">
-        <v>13</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="L52" t="n">
-        <v>79</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="M52" t="n">
-        <v>20</v>
+        <v>99</v>
+      </c>
+      <c r="N52" t="n">
+        <v>27</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="R52" t="n">
+        <v>81</v>
+      </c>
+      <c r="S52" t="n">
+        <v>12</v>
+      </c>
+      <c r="T52" t="n">
+        <v>84</v>
+      </c>
+      <c r="U52" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -3463,28 +5143,52 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.484375</v>
+        <v>0.46875</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4789650037230082</v>
+        <v>0.46875</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4877373846988605</v>
+        <v>95</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4264852306671092</v>
+        <v>161</v>
       </c>
       <c r="J53" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.8105263157894737</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.6015625</v>
+      </c>
+      <c r="M53" t="n">
+        <v>97</v>
+      </c>
+      <c r="N53" t="n">
+        <v>31</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.134020618556701</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.203125</v>
+      </c>
+      <c r="R53" t="n">
         <v>77</v>
       </c>
-      <c r="K53" t="n">
+      <c r="S53" t="n">
         <v>18</v>
       </c>
-      <c r="L53" t="n">
-        <v>81</v>
-      </c>
-      <c r="M53" t="n">
-        <v>16</v>
+      <c r="T53" t="n">
+        <v>84</v>
+      </c>
+      <c r="U53" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -3509,25 +5213,49 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5515257192676548</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5320951449983707</v>
+        <v>99</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4883101150817686</v>
+        <v>147</v>
       </c>
       <c r="J54" t="n">
-        <v>83</v>
+        <v>0.5374149659863946</v>
       </c>
       <c r="K54" t="n">
-        <v>16</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="L54" t="n">
-        <v>72</v>
+        <v>0.6422764227642278</v>
       </c>
       <c r="M54" t="n">
-        <v>21</v>
+        <v>93</v>
+      </c>
+      <c r="N54" t="n">
+        <v>45</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.2688172043010753</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.3623188405797101</v>
+      </c>
+      <c r="R54" t="n">
+        <v>79</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="n">
+        <v>68</v>
+      </c>
+      <c r="U54" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="55">
@@ -3549,28 +5277,52 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4944717444717445</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H55" t="n">
-        <v>0.496078431372549</v>
+        <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4474502129618971</v>
+        <v>150</v>
       </c>
       <c r="J55" t="n">
-        <v>69</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>21</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="L55" t="n">
-        <v>79</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="M55" t="n">
-        <v>23</v>
+        <v>102</v>
+      </c>
+      <c r="N55" t="n">
+        <v>42</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.196078431372549</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="R55" t="n">
+        <v>68</v>
+      </c>
+      <c r="S55" t="n">
+        <v>22</v>
+      </c>
+      <c r="T55" t="n">
+        <v>82</v>
+      </c>
+      <c r="U55" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -3592,28 +5344,52 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4729965156794425</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4865392965696917</v>
+        <v>94</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4093761535622001</v>
+        <v>157</v>
       </c>
       <c r="J56" t="n">
+        <v>0.4968152866242038</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.6215139442231075</v>
+      </c>
+      <c r="M56" t="n">
+        <v>98</v>
+      </c>
+      <c r="N56" t="n">
+        <v>35</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.1938775510204082</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R56" t="n">
+        <v>78</v>
+      </c>
+      <c r="S56" t="n">
+        <v>16</v>
+      </c>
+      <c r="T56" t="n">
         <v>79</v>
       </c>
-      <c r="K56" t="n">
-        <v>15</v>
-      </c>
-      <c r="L56" t="n">
-        <v>85</v>
-      </c>
-      <c r="M56" t="n">
-        <v>13</v>
+      <c r="U56" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -3635,28 +5411,52 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4074832464631423</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4460661964188822</v>
+        <v>95</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3801406028422291</v>
+        <v>146</v>
       </c>
       <c r="J57" t="n">
-        <v>73</v>
+        <v>0.4726027397260274</v>
       </c>
       <c r="K57" t="n">
-        <v>22</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="L57" t="n">
-        <v>85</v>
+        <v>0.5726141078838175</v>
       </c>
       <c r="M57" t="n">
-        <v>12</v>
+        <v>97</v>
+      </c>
+      <c r="N57" t="n">
+        <v>46</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.2061855670103093</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.2797202797202797</v>
+      </c>
+      <c r="R57" t="n">
+        <v>69</v>
+      </c>
+      <c r="S57" t="n">
+        <v>26</v>
+      </c>
+      <c r="T57" t="n">
+        <v>77</v>
+      </c>
+      <c r="U57" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -3678,28 +5478,52 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4851190476190476</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4934718746599935</v>
+        <v>91</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4010193050193051</v>
+        <v>152</v>
       </c>
       <c r="J58" t="n">
-        <v>79</v>
+        <v>0.4868421052631579</v>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>0.8131868131868132</v>
       </c>
       <c r="L58" t="n">
-        <v>89</v>
+        <v>0.6090534979423868</v>
       </c>
       <c r="M58" t="n">
-        <v>12</v>
+        <v>101</v>
+      </c>
+      <c r="N58" t="n">
+        <v>40</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.2277227722772277</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.3262411347517731</v>
+      </c>
+      <c r="R58" t="n">
+        <v>74</v>
+      </c>
+      <c r="S58" t="n">
+        <v>17</v>
+      </c>
+      <c r="T58" t="n">
+        <v>78</v>
+      </c>
+      <c r="U58" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="59">
@@ -3721,28 +5545,52 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5052631578947369</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5034965034965034</v>
+        <v>88</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4444444444444444</v>
+        <v>169</v>
       </c>
       <c r="J59" t="n">
-        <v>70</v>
+        <v>0.4733727810650887</v>
       </c>
       <c r="K59" t="n">
-        <v>18</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L59" t="n">
-        <v>82</v>
+        <v>0.622568093385214</v>
       </c>
       <c r="M59" t="n">
-        <v>22</v>
+        <v>104</v>
+      </c>
+      <c r="N59" t="n">
+        <v>23</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.1442307692307692</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.2362204724409449</v>
+      </c>
+      <c r="R59" t="n">
+        <v>80</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8</v>
+      </c>
+      <c r="T59" t="n">
+        <v>89</v>
+      </c>
+      <c r="U59" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -3764,28 +5612,52 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.546875</v>
       </c>
       <c r="G60" t="n">
-        <v>0.516507703595011</v>
+        <v>0.546875</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5125125125125125</v>
+        <v>111</v>
       </c>
       <c r="I60" t="n">
-        <v>0.49609375</v>
+        <v>152</v>
       </c>
       <c r="J60" t="n">
-        <v>85</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="K60" t="n">
-        <v>26</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="L60" t="n">
-        <v>60</v>
+        <v>0.6692015209125476</v>
       </c>
       <c r="M60" t="n">
-        <v>21</v>
+        <v>81</v>
+      </c>
+      <c r="N60" t="n">
+        <v>40</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.2098765432098765</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.2809917355371901</v>
+      </c>
+      <c r="R60" t="n">
+        <v>88</v>
+      </c>
+      <c r="S60" t="n">
+        <v>23</v>
+      </c>
+      <c r="T60" t="n">
+        <v>64</v>
+      </c>
+      <c r="U60" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -3807,28 +5679,52 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4914285714285714</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4941380807642206</v>
+        <v>98</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4535104364326376</v>
+        <v>159</v>
       </c>
       <c r="J61" t="n">
+        <v>0.5220125786163522</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.8469387755102041</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.6459143968871596</v>
+      </c>
+      <c r="M61" t="n">
+        <v>94</v>
+      </c>
+      <c r="N61" t="n">
+        <v>33</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.1914893617021277</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.2834645669291339</v>
+      </c>
+      <c r="R61" t="n">
+        <v>83</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="n">
         <v>76</v>
       </c>
-      <c r="K61" t="n">
-        <v>22</v>
-      </c>
-      <c r="L61" t="n">
-        <v>74</v>
-      </c>
-      <c r="M61" t="n">
-        <v>20</v>
+      <c r="U61" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -3850,28 +5746,52 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5085470085470085</v>
+        <v>0.5625</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5055945590171128</v>
+        <v>106</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4721853281853282</v>
+        <v>138</v>
       </c>
       <c r="J62" t="n">
-        <v>85</v>
+        <v>0.5797101449275363</v>
       </c>
       <c r="K62" t="n">
-        <v>21</v>
+        <v>0.7547169811320755</v>
       </c>
       <c r="L62" t="n">
-        <v>68</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="M62" t="n">
-        <v>18</v>
+        <v>86</v>
+      </c>
+      <c r="N62" t="n">
+        <v>54</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R62" t="n">
+        <v>80</v>
+      </c>
+      <c r="S62" t="n">
+        <v>26</v>
+      </c>
+      <c r="T62" t="n">
+        <v>58</v>
+      </c>
+      <c r="U62" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="63">
@@ -3893,28 +5813,52 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4653705062362435</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4742132867132867</v>
+        <v>88</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4269959923826848</v>
+        <v>136</v>
       </c>
       <c r="J63" t="n">
-        <v>64</v>
+        <v>0.4558823529411765</v>
       </c>
       <c r="K63" t="n">
-        <v>24</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="L63" t="n">
-        <v>81</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="M63" t="n">
-        <v>23</v>
+        <v>104</v>
+      </c>
+      <c r="N63" t="n">
+        <v>56</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.3749999999999999</v>
+      </c>
+      <c r="R63" t="n">
+        <v>62</v>
+      </c>
+      <c r="S63" t="n">
+        <v>26</v>
+      </c>
+      <c r="T63" t="n">
+        <v>74</v>
+      </c>
+      <c r="U63" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3936,28 +5880,52 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4399940440738535</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="H64" t="n">
-        <v>0.4561527581329562</v>
+        <v>91</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4103160251442349</v>
+        <v>137</v>
       </c>
       <c r="J64" t="n">
-        <v>65</v>
+        <v>0.4452554744525548</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>0.6703296703296703</v>
       </c>
       <c r="L64" t="n">
-        <v>81</v>
+        <v>0.5350877192982455</v>
       </c>
       <c r="M64" t="n">
-        <v>20</v>
+        <v>101</v>
+      </c>
+      <c r="N64" t="n">
+        <v>55</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.2475247524752475</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.3205128205128205</v>
+      </c>
+      <c r="R64" t="n">
+        <v>61</v>
+      </c>
+      <c r="S64" t="n">
+        <v>30</v>
+      </c>
+      <c r="T64" t="n">
+        <v>76</v>
+      </c>
+      <c r="U64" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -3979,28 +5947,52 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.453125</v>
+        <v>0.46875</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4311346548188654</v>
+        <v>0.46875</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4562669560499186</v>
+        <v>95</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4002677376171352</v>
+        <v>145</v>
       </c>
       <c r="J65" t="n">
-        <v>72</v>
+        <v>0.4758620689655172</v>
       </c>
       <c r="K65" t="n">
-        <v>23</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="L65" t="n">
-        <v>82</v>
+        <v>0.575</v>
       </c>
       <c r="M65" t="n">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="N65" t="n">
+        <v>47</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.2164948453608248</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="R65" t="n">
+        <v>69</v>
+      </c>
+      <c r="S65" t="n">
+        <v>26</v>
+      </c>
+      <c r="T65" t="n">
+        <v>76</v>
+      </c>
+      <c r="U65" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="66">
@@ -4022,28 +6014,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G66" t="n">
-        <v>0.478125</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4876202055930142</v>
+        <v>83</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4004027668330269</v>
+        <v>160</v>
       </c>
       <c r="J66" t="n">
-        <v>68</v>
+        <v>0.4375</v>
       </c>
       <c r="K66" t="n">
-        <v>15</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="L66" t="n">
-        <v>92</v>
+        <v>0.5761316872427984</v>
       </c>
       <c r="M66" t="n">
-        <v>17</v>
+        <v>109</v>
+      </c>
+      <c r="N66" t="n">
+        <v>32</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.1743119266055046</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.2695035460992908</v>
+      </c>
+      <c r="R66" t="n">
+        <v>70</v>
+      </c>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
+        <v>90</v>
+      </c>
+      <c r="U66" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -4065,28 +6081,52 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4989010989010989</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4991304347826087</v>
+        <v>92</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4664246823956443</v>
+        <v>135</v>
       </c>
       <c r="J67" t="n">
-        <v>67</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="K67" t="n">
-        <v>25</v>
+        <v>0.7065217391304348</v>
       </c>
       <c r="L67" t="n">
-        <v>73</v>
+        <v>0.5726872246696035</v>
       </c>
       <c r="M67" t="n">
+        <v>100</v>
+      </c>
+      <c r="N67" t="n">
+        <v>57</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.3821656050955414</v>
+      </c>
+      <c r="R67" t="n">
+        <v>65</v>
+      </c>
+      <c r="S67" t="n">
         <v>27</v>
+      </c>
+      <c r="T67" t="n">
+        <v>70</v>
+      </c>
+      <c r="U67" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="68">
@@ -4108,28 +6148,52 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5453884671297045</v>
+        <v>0.515625</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5305036908380374</v>
+        <v>98</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4916555109326194</v>
+        <v>159</v>
       </c>
       <c r="J68" t="n">
-        <v>80</v>
+        <v>0.5157232704402516</v>
       </c>
       <c r="K68" t="n">
-        <v>18</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="L68" t="n">
-        <v>71</v>
+        <v>0.6381322957198443</v>
       </c>
       <c r="M68" t="n">
-        <v>23</v>
+        <v>94</v>
+      </c>
+      <c r="N68" t="n">
+        <v>33</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.1808510638297872</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.2677165354330709</v>
+      </c>
+      <c r="R68" t="n">
+        <v>82</v>
+      </c>
+      <c r="S68" t="n">
+        <v>16</v>
+      </c>
+      <c r="T68" t="n">
+        <v>77</v>
+      </c>
+      <c r="U68" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="69">
@@ -4151,28 +6215,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4108787263930077</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="H69" t="n">
-        <v>0.4380156317846287</v>
+        <v>94</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3891953419140181</v>
+        <v>160</v>
       </c>
       <c r="J69" t="n">
-        <v>67</v>
+        <v>0.4625</v>
       </c>
       <c r="K69" t="n">
-        <v>27</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="L69" t="n">
-        <v>82</v>
+        <v>0.5826771653543308</v>
       </c>
       <c r="M69" t="n">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="N69" t="n">
+        <v>32</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.1846153846153846</v>
+      </c>
+      <c r="R69" t="n">
+        <v>74</v>
+      </c>
+      <c r="S69" t="n">
+        <v>20</v>
+      </c>
+      <c r="T69" t="n">
+        <v>86</v>
+      </c>
+      <c r="U69" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -4194,28 +6282,52 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5210884353741496</v>
+        <v>0.484375</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5154194760694153</v>
+        <v>83</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4579333709768493</v>
+        <v>150</v>
       </c>
       <c r="J70" t="n">
-        <v>65</v>
+        <v>0.4466666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>18</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="L70" t="n">
-        <v>82</v>
+        <v>0.5751072961373391</v>
       </c>
       <c r="M70" t="n">
-        <v>27</v>
+        <v>109</v>
+      </c>
+      <c r="N70" t="n">
+        <v>42</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.2385321100917431</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.3443708609271523</v>
+      </c>
+      <c r="R70" t="n">
+        <v>67</v>
+      </c>
+      <c r="S70" t="n">
+        <v>16</v>
+      </c>
+      <c r="T70" t="n">
+        <v>83</v>
+      </c>
+      <c r="U70" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="71">
@@ -4240,25 +6352,49 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>0.5696145124716554</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5500162919517758</v>
+        <v>93</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5111111111111111</v>
+        <v>143</v>
       </c>
       <c r="J71" t="n">
-        <v>76</v>
+        <v>0.5174825174825175</v>
       </c>
       <c r="K71" t="n">
-        <v>17</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="L71" t="n">
-        <v>71</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="M71" t="n">
-        <v>28</v>
+        <v>99</v>
+      </c>
+      <c r="N71" t="n">
+        <v>49</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.6122448979591837</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="R71" t="n">
+        <v>74</v>
+      </c>
+      <c r="S71" t="n">
+        <v>19</v>
+      </c>
+      <c r="T71" t="n">
+        <v>69</v>
+      </c>
+      <c r="U71" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="72">
@@ -4283,25 +6419,49 @@
         <v>0.5</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4807256235827664</v>
+        <v>0.5</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4861277336524861</v>
+        <v>101</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4535104364326376</v>
+        <v>149</v>
       </c>
       <c r="J72" t="n">
-        <v>76</v>
+        <v>0.5167785234899329</v>
       </c>
       <c r="K72" t="n">
-        <v>25</v>
+        <v>0.7623762376237624</v>
       </c>
       <c r="L72" t="n">
-        <v>71</v>
+        <v>0.616</v>
       </c>
       <c r="M72" t="n">
-        <v>20</v>
+        <v>91</v>
+      </c>
+      <c r="N72" t="n">
+        <v>43</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.4418604651162791</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.2087912087912088</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.2835820895522388</v>
+      </c>
+      <c r="R72" t="n">
+        <v>77</v>
+      </c>
+      <c r="S72" t="n">
+        <v>24</v>
+      </c>
+      <c r="T72" t="n">
+        <v>72</v>
+      </c>
+      <c r="U72" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -4323,28 +6483,52 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.484375</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4927401340282949</v>
+        <v>0.484375</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4957307060755337</v>
+        <v>105</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4509631398673914</v>
+        <v>160</v>
       </c>
       <c r="J73" t="n">
-        <v>86</v>
+        <v>0.51875</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>0.7904761904761904</v>
       </c>
       <c r="L73" t="n">
-        <v>72</v>
+        <v>0.6264150943396226</v>
       </c>
       <c r="M73" t="n">
-        <v>15</v>
+        <v>87</v>
+      </c>
+      <c r="N73" t="n">
+        <v>32</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.1149425287356322</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.1680672268907563</v>
+      </c>
+      <c r="R73" t="n">
+        <v>83</v>
+      </c>
+      <c r="S73" t="n">
+        <v>22</v>
+      </c>
+      <c r="T73" t="n">
+        <v>77</v>
+      </c>
+      <c r="U73" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -4366,28 +6550,52 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.484375</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5066445182724253</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5059523809523809</v>
+        <v>84</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4781319495922906</v>
+        <v>143</v>
       </c>
       <c r="J74" t="n">
-        <v>57</v>
+        <v>0.4335664335664335</v>
       </c>
       <c r="K74" t="n">
+        <v>0.7380952380952381</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.5462555066079295</v>
+      </c>
+      <c r="M74" t="n">
+        <v>108</v>
+      </c>
+      <c r="N74" t="n">
+        <v>49</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.5510204081632653</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.3439490445859872</v>
+      </c>
+      <c r="R74" t="n">
+        <v>62</v>
+      </c>
+      <c r="S74" t="n">
+        <v>22</v>
+      </c>
+      <c r="T74" t="n">
+        <v>81</v>
+      </c>
+      <c r="U74" t="n">
         <v>27</v>
-      </c>
-      <c r="L74" t="n">
-        <v>72</v>
-      </c>
-      <c r="M74" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="75">
@@ -4412,25 +6620,49 @@
         <v>0.5104166666666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5051612081050083</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5043988269794721</v>
+        <v>99</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4882032667876589</v>
+        <v>139</v>
       </c>
       <c r="J75" t="n">
-        <v>69</v>
+        <v>0.5179856115107914</v>
       </c>
       <c r="K75" t="n">
-        <v>30</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L75" t="n">
-        <v>64</v>
+        <v>0.6050420168067226</v>
       </c>
       <c r="M75" t="n">
-        <v>29</v>
+        <v>93</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.4905660377358491</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.2795698924731183</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.3561643835616438</v>
+      </c>
+      <c r="R75" t="n">
+        <v>72</v>
+      </c>
+      <c r="S75" t="n">
+        <v>27</v>
+      </c>
+      <c r="T75" t="n">
+        <v>67</v>
+      </c>
+      <c r="U75" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="76">
@@ -4452,28 +6684,52 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5267094017094017</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5162919517758228</v>
+        <v>99</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4688554491564068</v>
+        <v>154</v>
       </c>
       <c r="J76" t="n">
-        <v>82</v>
+        <v>0.512987012987013</v>
       </c>
       <c r="K76" t="n">
-        <v>17</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="L76" t="n">
-        <v>74</v>
+        <v>0.6245059288537549</v>
       </c>
       <c r="M76" t="n">
-        <v>19</v>
+        <v>93</v>
+      </c>
+      <c r="N76" t="n">
+        <v>38</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.2748091603053435</v>
+      </c>
+      <c r="R76" t="n">
+        <v>79</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="n">
+        <v>75</v>
+      </c>
+      <c r="U76" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="77">
@@ -4495,28 +6751,52 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4868421052631579</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4916440586001085</v>
+        <v>97</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4421112542311956</v>
+        <v>141</v>
       </c>
       <c r="J77" t="n">
-        <v>77</v>
+        <v>0.4964539007092199</v>
       </c>
       <c r="K77" t="n">
-        <v>20</v>
+        <v>0.7216494845360825</v>
       </c>
       <c r="L77" t="n">
-        <v>77</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="M77" t="n">
-        <v>18</v>
+        <v>95</v>
+      </c>
+      <c r="N77" t="n">
+        <v>51</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.2526315789473684</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.3287671232876713</v>
+      </c>
+      <c r="R77" t="n">
+        <v>70</v>
+      </c>
+      <c r="S77" t="n">
+        <v>27</v>
+      </c>
+      <c r="T77" t="n">
+        <v>71</v>
+      </c>
+      <c r="U77" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -4538,27 +6818,51 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5320298430666324</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5138471805138471</v>
+        <v>111</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4593406593406594</v>
+        <v>160</v>
       </c>
       <c r="J78" t="n">
-        <v>99</v>
+        <v>0.5625</v>
       </c>
       <c r="K78" t="n">
-        <v>12</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="L78" t="n">
+        <v>0.6642066420664205</v>
+      </c>
+      <c r="M78" t="n">
+        <v>81</v>
+      </c>
+      <c r="N78" t="n">
+        <v>32</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.1358024691358025</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="R78" t="n">
+        <v>90</v>
+      </c>
+      <c r="S78" t="n">
+        <v>21</v>
+      </c>
+      <c r="T78" t="n">
         <v>70</v>
       </c>
-      <c r="M78" t="n">
+      <c r="U78" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4581,27 +6885,51 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G79" t="n">
-        <v>0.515764008116123</v>
+        <v>0.515625</v>
       </c>
       <c r="H79" t="n">
-        <v>0.510963960052106</v>
+        <v>94</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4676473163470799</v>
+        <v>151</v>
       </c>
       <c r="J79" t="n">
-        <v>74</v>
+        <v>0.5033112582781457</v>
       </c>
       <c r="K79" t="n">
-        <v>20</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="L79" t="n">
+        <v>0.6204081632653061</v>
+      </c>
+      <c r="M79" t="n">
+        <v>98</v>
+      </c>
+      <c r="N79" t="n">
+        <v>41</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.2346938775510204</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.3309352517985611</v>
+      </c>
+      <c r="R79" t="n">
+        <v>76</v>
+      </c>
+      <c r="S79" t="n">
+        <v>18</v>
+      </c>
+      <c r="T79" t="n">
         <v>75</v>
       </c>
-      <c r="M79" t="n">
+      <c r="U79" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4624,28 +6952,52 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5433046683046683</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5308702791461413</v>
+        <v>87</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4790803941168071</v>
+        <v>136</v>
       </c>
       <c r="J80" t="n">
-        <v>70</v>
+        <v>0.4485294117647059</v>
       </c>
       <c r="K80" t="n">
-        <v>17</v>
+        <v>0.7011494252873564</v>
       </c>
       <c r="L80" t="n">
-        <v>78</v>
+        <v>0.547085201793722</v>
       </c>
       <c r="M80" t="n">
-        <v>27</v>
+        <v>105</v>
+      </c>
+      <c r="N80" t="n">
+        <v>56</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.3726708074534161</v>
+      </c>
+      <c r="R80" t="n">
+        <v>61</v>
+      </c>
+      <c r="S80" t="n">
+        <v>26</v>
+      </c>
+      <c r="T80" t="n">
+        <v>75</v>
+      </c>
+      <c r="U80" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="81">
@@ -4667,28 +7019,52 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.546875</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5019047619047619</v>
+        <v>0.546875</v>
       </c>
       <c r="H81" t="n">
-        <v>0.501304347826087</v>
+        <v>92</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4524502386218136</v>
+        <v>125</v>
       </c>
       <c r="J81" t="n">
-        <v>72</v>
+        <v>0.52</v>
       </c>
       <c r="K81" t="n">
-        <v>20</v>
+        <v>0.7065217391304348</v>
       </c>
       <c r="L81" t="n">
-        <v>78</v>
+        <v>0.599078341013825</v>
       </c>
       <c r="M81" t="n">
-        <v>22</v>
+        <v>100</v>
+      </c>
+      <c r="N81" t="n">
+        <v>67</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.5970149253731343</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.4790419161676647</v>
+      </c>
+      <c r="R81" t="n">
+        <v>65</v>
+      </c>
+      <c r="S81" t="n">
+        <v>27</v>
+      </c>
+      <c r="T81" t="n">
+        <v>60</v>
+      </c>
+      <c r="U81" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="82">
@@ -4710,28 +7086,52 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.46875</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4809437386569873</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H82" t="n">
-        <v>0.4814814814814815</v>
+        <v>84</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4678260869565218</v>
+        <v>130</v>
       </c>
       <c r="J82" t="n">
-        <v>49</v>
+        <v>0.4461538461538462</v>
       </c>
       <c r="K82" t="n">
-        <v>35</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="L82" t="n">
-        <v>67</v>
+        <v>0.5420560747663552</v>
       </c>
       <c r="M82" t="n">
-        <v>41</v>
+        <v>108</v>
+      </c>
+      <c r="N82" t="n">
+        <v>62</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.4235294117647058</v>
+      </c>
+      <c r="R82" t="n">
+        <v>58</v>
+      </c>
+      <c r="S82" t="n">
+        <v>26</v>
+      </c>
+      <c r="T82" t="n">
+        <v>72</v>
+      </c>
+      <c r="U82" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="83">
@@ -4753,28 +7153,52 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4771018455228981</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4854537559704733</v>
+        <v>94</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4307400379506642</v>
+        <v>150</v>
       </c>
       <c r="J83" t="n">
-        <v>74</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="K83" t="n">
-        <v>20</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="L83" t="n">
-        <v>80</v>
+        <v>0.5983606557377049</v>
       </c>
       <c r="M83" t="n">
-        <v>18</v>
+        <v>98</v>
+      </c>
+      <c r="N83" t="n">
+        <v>42</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R83" t="n">
+        <v>73</v>
+      </c>
+      <c r="S83" t="n">
+        <v>21</v>
+      </c>
+      <c r="T83" t="n">
+        <v>77</v>
+      </c>
+      <c r="U83" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="84">
@@ -4796,28 +7220,52 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5625</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5587269872984159</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5448892767535726</v>
+        <v>103</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5249204665959704</v>
+        <v>146</v>
       </c>
       <c r="J84" t="n">
-        <v>81</v>
+        <v>0.5684931506849316</v>
       </c>
       <c r="K84" t="n">
-        <v>22</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="L84" t="n">
-        <v>62</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="M84" t="n">
-        <v>27</v>
+        <v>89</v>
+      </c>
+      <c r="N84" t="n">
+        <v>46</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.2921348314606741</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.3851851851851852</v>
+      </c>
+      <c r="R84" t="n">
+        <v>83</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20</v>
+      </c>
+      <c r="T84" t="n">
+        <v>63</v>
+      </c>
+      <c r="U84" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="85">
@@ -4839,28 +7287,52 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.484375</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4549752611324904</v>
+        <v>107</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4163771712158809</v>
+        <v>150</v>
       </c>
       <c r="J85" t="n">
-        <v>81</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="K85" t="n">
-        <v>26</v>
+        <v>0.7383177570093458</v>
       </c>
       <c r="L85" t="n">
-        <v>72</v>
+        <v>0.6147859922178988</v>
       </c>
       <c r="M85" t="n">
-        <v>13</v>
+        <v>85</v>
+      </c>
+      <c r="N85" t="n">
+        <v>42</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.1647058823529412</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.2204724409448819</v>
+      </c>
+      <c r="R85" t="n">
+        <v>79</v>
+      </c>
+      <c r="S85" t="n">
+        <v>28</v>
+      </c>
+      <c r="T85" t="n">
+        <v>71</v>
+      </c>
+      <c r="U85" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -4882,28 +7354,52 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4561728395061729</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4768251550429768</v>
+        <v>101</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4147629073311756</v>
+        <v>159</v>
       </c>
       <c r="J86" t="n">
-        <v>83</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="K86" t="n">
-        <v>18</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="L86" t="n">
-        <v>79</v>
+        <v>0.6230769230769232</v>
       </c>
       <c r="M86" t="n">
-        <v>12</v>
+        <v>91</v>
+      </c>
+      <c r="N86" t="n">
+        <v>33</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="R86" t="n">
+        <v>81</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="n">
+        <v>78</v>
+      </c>
+      <c r="U86" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -4928,25 +7424,49 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4455089820359281</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4753119913185024</v>
+        <v>97</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3939393939393939</v>
+        <v>163</v>
       </c>
       <c r="J87" t="n">
-        <v>82</v>
+        <v>0.4907975460122699</v>
       </c>
       <c r="K87" t="n">
-        <v>15</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="L87" t="n">
-        <v>85</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="M87" t="n">
-        <v>10</v>
+        <v>95</v>
+      </c>
+      <c r="N87" t="n">
+        <v>29</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="R87" t="n">
+        <v>80</v>
+      </c>
+      <c r="S87" t="n">
+        <v>17</v>
+      </c>
+      <c r="T87" t="n">
+        <v>83</v>
+      </c>
+      <c r="U87" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -4968,28 +7488,52 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5162337662337662</v>
+        <v>0.53125</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5103361984550103</v>
+        <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4688554491564068</v>
+        <v>167</v>
       </c>
       <c r="J88" t="n">
-        <v>82</v>
+        <v>0.5329341317365269</v>
       </c>
       <c r="K88" t="n">
-        <v>19</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="L88" t="n">
-        <v>72</v>
+        <v>0.6641791044776119</v>
       </c>
       <c r="M88" t="n">
-        <v>19</v>
+        <v>91</v>
+      </c>
+      <c r="N88" t="n">
+        <v>25</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.2241379310344828</v>
+      </c>
+      <c r="R88" t="n">
+        <v>89</v>
+      </c>
+      <c r="S88" t="n">
+        <v>12</v>
+      </c>
+      <c r="T88" t="n">
+        <v>78</v>
+      </c>
+      <c r="U88" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -5011,28 +7555,52 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.515625</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4928571428571429</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4950910875968146</v>
+        <v>103</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4612437015357692</v>
+        <v>136</v>
       </c>
       <c r="J89" t="n">
-        <v>80</v>
+        <v>0.5073529411764706</v>
       </c>
       <c r="K89" t="n">
-        <v>23</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="L89" t="n">
-        <v>70</v>
+        <v>0.5774058577405857</v>
       </c>
       <c r="M89" t="n">
-        <v>19</v>
+        <v>89</v>
+      </c>
+      <c r="N89" t="n">
+        <v>56</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.3928571428571428</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.247191011235955</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.303448275862069</v>
+      </c>
+      <c r="R89" t="n">
+        <v>69</v>
+      </c>
+      <c r="S89" t="n">
+        <v>34</v>
+      </c>
+      <c r="T89" t="n">
+        <v>67</v>
+      </c>
+      <c r="U89" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -5054,28 +7622,52 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.484375</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4543156059285092</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4715217391304348</v>
+        <v>100</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4221614227086183</v>
+        <v>152</v>
       </c>
       <c r="J90" t="n">
-        <v>78</v>
+        <v>0.506578947368421</v>
       </c>
       <c r="K90" t="n">
-        <v>22</v>
+        <v>0.77</v>
       </c>
       <c r="L90" t="n">
+        <v>0.611111111111111</v>
+      </c>
+      <c r="M90" t="n">
+        <v>92</v>
+      </c>
+      <c r="N90" t="n">
+        <v>40</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.1847826086956522</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.2575757575757576</v>
+      </c>
+      <c r="R90" t="n">
         <v>77</v>
       </c>
-      <c r="M90" t="n">
-        <v>15</v>
+      <c r="S90" t="n">
+        <v>23</v>
+      </c>
+      <c r="T90" t="n">
+        <v>75</v>
+      </c>
+      <c r="U90" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="91">
@@ -5097,28 +7689,52 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5165276950565814</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5121510673234811</v>
+        <v>105</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4881226971812</v>
+        <v>134</v>
       </c>
       <c r="J91" t="n">
-        <v>81</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="K91" t="n">
-        <v>24</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L91" t="n">
-        <v>65</v>
+        <v>0.6443514644351463</v>
       </c>
       <c r="M91" t="n">
-        <v>22</v>
+        <v>87</v>
+      </c>
+      <c r="N91" t="n">
+        <v>58</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="R91" t="n">
+        <v>77</v>
+      </c>
+      <c r="S91" t="n">
+        <v>28</v>
+      </c>
+      <c r="T91" t="n">
+        <v>57</v>
+      </c>
+      <c r="U91" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="92">
@@ -5140,28 +7756,52 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.546875</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5238884045335659</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5150285212812638</v>
+        <v>106</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4796747967479675</v>
+        <v>157</v>
       </c>
       <c r="J92" t="n">
-        <v>87</v>
+        <v>0.5477707006369427</v>
       </c>
       <c r="K92" t="n">
-        <v>19</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="L92" t="n">
-        <v>68</v>
+        <v>0.6539923954372624</v>
       </c>
       <c r="M92" t="n">
-        <v>18</v>
+        <v>86</v>
+      </c>
+      <c r="N92" t="n">
+        <v>35</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.1744186046511628</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.2479338842975207</v>
+      </c>
+      <c r="R92" t="n">
+        <v>86</v>
+      </c>
+      <c r="S92" t="n">
+        <v>20</v>
+      </c>
+      <c r="T92" t="n">
+        <v>71</v>
+      </c>
+      <c r="U92" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -5183,28 +7823,52 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.484375</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G93" t="n">
-        <v>0.428125</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H93" t="n">
-        <v>0.4598560052361732</v>
+        <v>103</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4026961631524369</v>
+        <v>162</v>
       </c>
       <c r="J93" t="n">
-        <v>82</v>
+        <v>0.5246913580246914</v>
       </c>
       <c r="K93" t="n">
-        <v>21</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="L93" t="n">
-        <v>78</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="M93" t="n">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="N93" t="n">
+        <v>30</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.1348314606741573</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.2016806722689076</v>
+      </c>
+      <c r="R93" t="n">
+        <v>85</v>
+      </c>
+      <c r="S93" t="n">
+        <v>18</v>
+      </c>
+      <c r="T93" t="n">
+        <v>77</v>
+      </c>
+      <c r="U93" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -5226,28 +7890,52 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G94" t="n">
-        <v>0.49599278701663</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4978146853146853</v>
+        <v>104</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4459489456159823</v>
+        <v>159</v>
       </c>
       <c r="J94" t="n">
-        <v>87</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="K94" t="n">
-        <v>17</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="L94" t="n">
-        <v>74</v>
+        <v>0.6387832699619772</v>
       </c>
       <c r="M94" t="n">
-        <v>14</v>
+        <v>88</v>
+      </c>
+      <c r="N94" t="n">
+        <v>33</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.1477272727272727</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.2148760330578512</v>
+      </c>
+      <c r="R94" t="n">
+        <v>84</v>
+      </c>
+      <c r="S94" t="n">
+        <v>20</v>
+      </c>
+      <c r="T94" t="n">
+        <v>75</v>
+      </c>
+      <c r="U94" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -5269,28 +7957,52 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5625</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H95" t="n">
-        <v>0.5625</v>
+        <v>96</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5333333333333333</v>
+        <v>152</v>
       </c>
       <c r="J95" t="n">
-        <v>78</v>
+        <v>0.5328947368421053</v>
       </c>
       <c r="K95" t="n">
-        <v>18</v>
+        <v>0.84375</v>
       </c>
       <c r="L95" t="n">
-        <v>66</v>
+        <v>0.6532258064516129</v>
       </c>
       <c r="M95" t="n">
-        <v>30</v>
+        <v>96</v>
+      </c>
+      <c r="N95" t="n">
+        <v>40</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.3676470588235294</v>
+      </c>
+      <c r="R95" t="n">
+        <v>81</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="n">
+        <v>71</v>
+      </c>
+      <c r="U95" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="96">
@@ -5312,28 +8024,52 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4148148148148148</v>
+        <v>0.4375</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4550586191923578</v>
+        <v>94</v>
       </c>
       <c r="I96" t="n">
-        <v>0.37890625</v>
+        <v>146</v>
       </c>
       <c r="J96" t="n">
-        <v>75</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="K96" t="n">
-        <v>19</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="L96" t="n">
-        <v>87</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M96" t="n">
-        <v>11</v>
+        <v>98</v>
+      </c>
+      <c r="N96" t="n">
+        <v>46</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R96" t="n">
+        <v>66</v>
+      </c>
+      <c r="S96" t="n">
+        <v>28</v>
+      </c>
+      <c r="T96" t="n">
+        <v>80</v>
+      </c>
+      <c r="U96" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="97">
@@ -5355,28 +8091,52 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.515625</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5272584558298844</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5207338254450716</v>
+        <v>94</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4874709377421855</v>
+        <v>139</v>
       </c>
       <c r="J97" t="n">
+        <v>0.5179856115107914</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.6180257510729613</v>
+      </c>
+      <c r="M97" t="n">
+        <v>98</v>
+      </c>
+      <c r="N97" t="n">
+        <v>53</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.5849056603773585</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.3163265306122449</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.4105960264900662</v>
+      </c>
+      <c r="R97" t="n">
         <v>72</v>
       </c>
-      <c r="K97" t="n">
+      <c r="S97" t="n">
         <v>22</v>
       </c>
-      <c r="L97" t="n">
-        <v>71</v>
-      </c>
-      <c r="M97" t="n">
-        <v>27</v>
+      <c r="T97" t="n">
+        <v>67</v>
+      </c>
+      <c r="U97" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="98">
@@ -5398,28 +8158,52 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.46875</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4794520547945206</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H98" t="n">
-        <v>0.4849673202614379</v>
+        <v>90</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4393037104901512</v>
+        <v>161</v>
       </c>
       <c r="J98" t="n">
-        <v>67</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K98" t="n">
-        <v>23</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="L98" t="n">
-        <v>79</v>
+        <v>0.6135458167330677</v>
       </c>
       <c r="M98" t="n">
-        <v>23</v>
+        <v>102</v>
+      </c>
+      <c r="N98" t="n">
+        <v>31</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.2706766917293233</v>
+      </c>
+      <c r="R98" t="n">
+        <v>77</v>
+      </c>
+      <c r="S98" t="n">
+        <v>13</v>
+      </c>
+      <c r="T98" t="n">
+        <v>84</v>
+      </c>
+      <c r="U98" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="99">
@@ -5441,28 +8225,52 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4874078624078624</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4910782287019911</v>
+        <v>101</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4573850959393128</v>
+        <v>153</v>
       </c>
       <c r="J99" t="n">
-        <v>77</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="K99" t="n">
-        <v>24</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="L99" t="n">
-        <v>71</v>
+        <v>0.6377952755905512</v>
       </c>
       <c r="M99" t="n">
+        <v>91</v>
+      </c>
+      <c r="N99" t="n">
+        <v>39</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.4871794871794872</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.2087912087912088</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.2923076923076923</v>
+      </c>
+      <c r="R99" t="n">
+        <v>81</v>
+      </c>
+      <c r="S99" t="n">
         <v>20</v>
+      </c>
+      <c r="T99" t="n">
+        <v>72</v>
+      </c>
+      <c r="U99" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -5484,28 +8292,52 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4495238095238095</v>
+        <v>0.4375</v>
       </c>
       <c r="H100" t="n">
-        <v>0.465359477124183</v>
+        <v>90</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4111111111111111</v>
+        <v>150</v>
       </c>
       <c r="J100" t="n">
-        <v>67</v>
+        <v>0.44</v>
       </c>
       <c r="K100" t="n">
-        <v>23</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L100" t="n">
-        <v>83</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M100" t="n">
-        <v>19</v>
+        <v>102</v>
+      </c>
+      <c r="N100" t="n">
+        <v>42</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R100" t="n">
+        <v>66</v>
+      </c>
+      <c r="S100" t="n">
+        <v>24</v>
+      </c>
+      <c r="T100" t="n">
+        <v>84</v>
+      </c>
+      <c r="U100" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -5527,28 +8359,52 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4496724240619416</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4633087277464177</v>
+        <v>98</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4266978922716628</v>
+        <v>132</v>
       </c>
       <c r="J101" t="n">
-        <v>71</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="K101" t="n">
-        <v>27</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L101" t="n">
-        <v>75</v>
+        <v>0.5478260869565218</v>
       </c>
       <c r="M101" t="n">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="N101" t="n">
+        <v>60</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.2659574468085106</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.3246753246753247</v>
+      </c>
+      <c r="R101" t="n">
+        <v>63</v>
+      </c>
+      <c r="S101" t="n">
+        <v>35</v>
+      </c>
+      <c r="T101" t="n">
+        <v>69</v>
+      </c>
+      <c r="U101" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -5584,10 +8440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7478</v>
+        <v>7403</v>
       </c>
       <c r="C2" t="n">
-        <v>2076</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="3">
@@ -5597,10 +8453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7620</v>
+        <v>7524</v>
       </c>
       <c r="C3" t="n">
-        <v>2026</v>
+        <v>2122</v>
       </c>
     </row>
   </sheetData>
@@ -5651,16 +8507,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>357</v>
+      </c>
+      <c r="E2" t="n">
         <v>56</v>
-      </c>
-      <c r="D2" t="n">
-        <v>359</v>
-      </c>
-      <c r="E2" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -5670,10 +8526,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
         <v>347</v>
@@ -5689,16 +8545,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>518</v>
+        <v>414</v>
       </c>
       <c r="C4" t="n">
-        <v>303</v>
+        <v>407</v>
       </c>
       <c r="D4" t="n">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -5708,16 +8564,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C5" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" t="n">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
@@ -5727,16 +8583,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D6" t="n">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -5746,16 +8602,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -5765,16 +8621,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>734</v>
+        <v>768</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -5784,16 +8640,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D9" t="n">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E9" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -5803,16 +8659,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -5822,16 +8678,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="C11" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="D11" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E11" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5841,16 +8697,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="E12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -5860,16 +8716,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>540</v>
+        <v>583</v>
       </c>
       <c r="C13" t="n">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="D13" t="n">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="E13" t="n">
-        <v>267</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
@@ -5879,16 +8735,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C14" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D14" t="n">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="E14" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
